--- a/MU/Test upload format/Normal/2025 - 2026/CP1 25-26.xlsx
+++ b/MU/Test upload format/Normal/2025 - 2026/CP1 25-26.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$18</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="55">
   <si>
     <t>custid</t>
   </si>
@@ -86,40 +89,112 @@
     <t>modifiedloancat</t>
   </si>
   <si>
-    <t>cust01</t>
-  </si>
-  <si>
-    <t>cust01AC01new</t>
+    <t>HomeStay</t>
+  </si>
+  <si>
+    <t>CR13Q1252601</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>01-04-2025</t>
   </si>
   <si>
     <t>10000</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>40000</t>
-  </si>
-  <si>
-    <t>01-04-2025</t>
-  </si>
-  <si>
-    <t>2000001</t>
+    <t>J</t>
+  </si>
+  <si>
+    <t>CR13Q1252602</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>CR13Q1252603</t>
+  </si>
+  <si>
+    <t>100</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
+    <t>01-04-2026</t>
+  </si>
+  <si>
+    <t>100001</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>CR13Q1252604</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>CR13Q1252605</t>
+  </si>
+  <si>
+    <t>1000003</t>
+  </si>
+  <si>
     <t>TP</t>
   </si>
   <si>
-    <t>cust06</t>
-  </si>
-  <si>
-    <t>cust01AC06new</t>
-  </si>
-  <si>
-    <t>1900001</t>
+    <t>CR13Q1252606</t>
+  </si>
+  <si>
+    <t>CR13Q1252607</t>
+  </si>
+  <si>
+    <t>CR13Q1252608</t>
+  </si>
+  <si>
+    <t>CR13Q1252609</t>
+  </si>
+  <si>
+    <t>1000007</t>
+  </si>
+  <si>
+    <t>CR13Q1252610</t>
+  </si>
+  <si>
+    <t>CR13Q1252611</t>
+  </si>
+  <si>
+    <t>CR13Q1252612</t>
+  </si>
+  <si>
+    <t>CR13Q1252613</t>
+  </si>
+  <si>
+    <t>1000011</t>
+  </si>
+  <si>
+    <t>CR13Q1252614</t>
+  </si>
+  <si>
+    <t>CR13Q1252615</t>
+  </si>
+  <si>
+    <t>CR13Q1252616</t>
+  </si>
+  <si>
+    <t>CR13Q1252617</t>
+  </si>
+  <si>
+    <t>300000</t>
   </si>
 </sst>
 </file>
@@ -132,7 +207,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,6 +222,12 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -493,7 +574,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -527,6 +608,21 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -645,135 +741,135 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -788,13 +884,16 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1114,8 +1213,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
+  <dimension ref="A1:T18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.8571428571429" customWidth="1"/>
     <col min="2" max="2" width="24.5714285714286" customWidth="1"/>
@@ -1131,9 +1230,10 @@
     <col min="13" max="13" width="18.5714285714286" customWidth="1"/>
     <col min="14" max="14" width="17.2857142857143" customWidth="1"/>
     <col min="15" max="15" width="13.2857142857143" customWidth="1"/>
+    <col min="18" max="19" width="16.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1191,106 +1291,844 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" customFormat="1" spans="1:19">
+    <row r="2" customFormat="1" spans="1:20">
       <c r="A2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="D2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2"/>
+      <c r="K2" s="11">
+        <v>1</v>
+      </c>
+      <c r="L2" s="11">
+        <v>1</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="9"/>
-      <c r="J2"/>
-      <c r="K2" s="9">
-        <v>1</v>
-      </c>
-      <c r="L2" s="9">
-        <v>1</v>
-      </c>
-      <c r="M2" s="10" t="s">
+      <c r="N2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="T2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="O2"/>
-      <c r="P2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>26</v>
-      </c>
-      <c r="R2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="G3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="11">
+        <v>1</v>
+      </c>
+      <c r="L3" s="11">
+        <v>1</v>
+      </c>
+      <c r="M3" s="7" t="s">
         <v>27</v>
       </c>
+      <c r="N3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="T3" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" spans="1:19">
-      <c r="A3" s="6" t="s">
+    <row r="4" spans="1:20">
+      <c r="A4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" s="11">
+        <v>1</v>
+      </c>
+      <c r="L4" s="11">
+        <v>1</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="T4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="11">
+        <v>1</v>
+      </c>
+      <c r="L5" s="11">
+        <v>1</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" s="11">
+        <v>1</v>
+      </c>
+      <c r="L6" s="11">
+        <v>1</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6" t="s">
+        <v>22</v>
+      </c>
+      <c r="S6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="T6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7" s="11">
+        <v>1</v>
+      </c>
+      <c r="L7" s="11">
+        <v>1</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="T7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8" s="11">
+        <v>1</v>
+      </c>
+      <c r="L8" s="11">
+        <v>1</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="T8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="G9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="11">
+        <v>1</v>
+      </c>
+      <c r="L9" s="11">
+        <v>1</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10" s="11">
+        <v>1</v>
+      </c>
+      <c r="L10" s="11">
+        <v>1</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P10" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" t="s">
+        <v>22</v>
+      </c>
+      <c r="S10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="T10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="9">
-        <v>1</v>
-      </c>
-      <c r="L3" s="9">
-        <v>1</v>
-      </c>
-      <c r="M3" s="10" t="s">
+      <c r="G11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="11">
+        <v>1</v>
+      </c>
+      <c r="L11" s="11">
+        <v>1</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S11" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="T11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="D12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12" s="11">
+        <v>1</v>
+      </c>
+      <c r="L12" s="11">
+        <v>1</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="T12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="P3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>26</v>
-      </c>
-      <c r="R3" t="s">
-        <v>22</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="G13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13" s="11">
+        <v>1</v>
+      </c>
+      <c r="L13" s="11">
+        <v>1</v>
+      </c>
+      <c r="M13" s="7" t="s">
         <v>27</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S13" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="7">
+        <v>10000</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="11">
+        <v>1</v>
+      </c>
+      <c r="L14" s="11">
+        <v>1</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P14" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>31</v>
+      </c>
+      <c r="R14" t="s">
+        <v>22</v>
+      </c>
+      <c r="S14" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="T14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15" s="11">
+        <v>1</v>
+      </c>
+      <c r="L15" s="11">
+        <v>1</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S15" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="T15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" s="11">
+        <v>1</v>
+      </c>
+      <c r="L16" s="11">
+        <v>1</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S16" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="T16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17" s="11">
+        <v>1</v>
+      </c>
+      <c r="L17" s="11">
+        <v>1</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S17" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="7">
+        <v>10000</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18" s="11">
+        <v>1</v>
+      </c>
+      <c r="L18" s="11">
+        <v>1</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P18" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>31</v>
+      </c>
+      <c r="R18" t="s">
+        <v>22</v>
+      </c>
+      <c r="S18" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="T18" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S18" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
